--- a/data_extactor/batch_10_fa/trimmed/batch_0001_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0001_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | شنیدن فعال | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | امور کارکنان و منابع انسانی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | فروش و بازاریابی | حقوق و مقررات دولتی | ارتباطات و رسانه</t>
+          <t>مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | اقتصاد و حسابداری | فروش و بازاریابی | قانون و دولت | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران مالی | مدیران کل و مدیران عملیات | مدیران منابع انسانی | تحلیل‌گران مدیریت و مشاوران سازمانی | مدیران فروش | خزانه‌داران و مدیران مالی و بودجه</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران امور مالی | مدیران کل و مدیران عملیات | مدیران منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران فروش | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | حقوق و مقررات دولتی | ارتباطات و رسانه | ساختمان و عمران | اقتصاد و حسابداری | جامعه‌شناسی و مردم‌شناسی | امور کارکنان و منابع انسانی</t>
+          <t>مدیریت و اداره | قانون و دولت | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اقتصاد و حسابداری | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ابتکار و اصالت</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تحلیل‌گران خط‌مشی تغییرات اقلیمی | مدیران انطباق با مقررات | کارشناسان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیط‌زیست از جمله بهداشت | تحلیل‌گران مدیریت و مشاوران سازمانی | کارشناسان پایداری سازمانی</t>
+          <t>تحلیل‌گران خط‌مشی تغییر اقلیم | مدیران تطبیق و نظارت مقرراتی | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان پایداری و توسعه پایدار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | تولید و فراوری | ریاضیات | امور کارکنان و منابع انسانی | اداری و دفتری | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | تولید و فرآوری | ریاضیات | پرسنل و منابع انسانی | اداری | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران عامل و مدیران ارشد اجرایی | مدیران امور پشتیبانی و تأسیسات | سرپرستان رده‌اول کارکنان امور دفتری و پشتیبانی اداری | مدیران تولید صنعتی | تحلیل‌گران مدیریت و مشاوران سازمانی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران تولید صنعتی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | مدیریت و امور اداری | ارتباطات و رسانه | اقتصاد و حسابداری | جامعه‌شناسی و مردم‌شناسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی</t>
+          <t>قانون و دولت | مدیریت و اداره | ارتباطات و رسانه | اقتصاد و حسابداری | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری و دادرسی | مدیران عامل و مدیران ارشد اجرایی | وکلا و حقوق‌دانان | مدرسان علوم سیاسی در آموزش عالی | دانشمندان علوم سیاسی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران عامل و مدیران ارشد اجرایی | وکلا | استادان علوم سیاسی دانشگاه | دانشمندان و پژوهشگران علوم سیاسی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتری و شخصی | مدیریت و اداره | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | اصالت | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | مدیران هنری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران هنری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | مدیریت و اداره | خدمات مشتری و شخصی | ارتباطات و رسانه | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | روانی کلام و سیالی ایده‌ها | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | روانی ایده‌ها | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | مدیران تبلیغات و روابط ترویجی | تحلیل‌گران هوش تجاری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | فعالان و بازرگانان تجارت الکترونیک | مدیران روابط عمومی | مدیران فروش</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | تحلیل‌گران هوش تجاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | مدیران روابط عمومی | مدیران فروش</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور کارکنان و منابع انسانی | رایانه و الکترونیک | ارتباطات و رسانه | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | رایانه و الکترونیک | ارتباطات و رسانه | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | فعالان و بازرگانان تجارت الکترونیک | کارشناسان فروش خدمات به‌استثنای تبلیغات، بیمه، مالی و گردشگری</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری | امور کارکنان و منابع انسانی | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>ارتباطات و رسانه | خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | پرسنل و منابع انسانی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و روابط ترویجی | مدیران جذب منابع مالی | مدیران منابع انسانی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران تأمین و برنامه‌ریزی رسانه‌ای | کارشناسان روابط عمومی</t>
+          <t>مدیران تبلیغات و روابط ترویجی | مدیران جذب منابع مالی و حامیان | مدیران منابع انسانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی و پخش رسانه | کارشناسان روابط عمومی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اداری و دفتری | فروش و بازاریابی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | اداری | فروش و بازاریابی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان جذب منابع مالی | مدیران بازاریابی | کارشناسان برنامه‌ریزی گردهمایی‌ها و همایش‌ها | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و عام‌المنفعه | خزانه‌داران و مدیران مالی و بودجه</t>
+          <t>کارشناسان جذب منابع مالی و حامی | مدیران بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و خدمات مردمی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اداری و دفتری | رایانه و الکترونیک | امور کارکنان و منابع انسانی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اداری | رایانه و الکترونیک | پرسنل و منابع انسانی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران انطباق با مقررات | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | مدیران امور پشتیبانی و تأسیسات | مدیران کل و مدیران عملیات | مدیران منابع انسانی | مسئولان دفاتر و کارشناسان اداری</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | مدیران امور ساختمان و تأسیسات | مدیران کل و مدیران عملیات | مدیران منابع انسانی | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
